--- a/testakten/kurpfalz-taxware-software-ip-insolvenz/02_Unternehmen_Produkt/06_SBOM_Open_Source.xlsx
+++ b/testakten/kurpfalz-taxware-software-ip-insolvenz/02_Unternehmen_Produkt/06_SBOM_Open_Source.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Komponenten" sheetId="1" r:id="Raaa767a374d84658"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scanbefunde" sheetId="2" r:id="Rde7a5a7827b34c43"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Policy_Stände" sheetId="3" r:id="R1e6779a481274b5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Komponenten" sheetId="1" r:id="R9c598cd5764a4610"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scanbefunde" sheetId="2" r:id="R62c07b0ae71c45ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Policy_Stände" sheetId="3" r:id="R214b84cd0d174e83"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/testakten/kurpfalz-taxware-software-ip-insolvenz/02_Unternehmen_Produkt/06_SBOM_Open_Source.xlsx
+++ b/testakten/kurpfalz-taxware-software-ip-insolvenz/02_Unternehmen_Produkt/06_SBOM_Open_Source.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Komponenten" sheetId="1" r:id="R9c598cd5764a4610"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scanbefunde" sheetId="2" r:id="R62c07b0ae71c45ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Policy_Stände" sheetId="3" r:id="R214b84cd0d174e83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Komponenten" sheetId="1" r:id="R7bbc40320cc9414a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scanbefunde" sheetId="2" r:id="R9748ecc4b6de4dab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Policy_Stände" sheetId="3" r:id="R60cae7e654444912"/>
   </x:sheets>
 </x:workbook>
 </file>
